--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -10177,13 +10177,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -11428,10 +11428,10 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>1</v>
@@ -12458,7 +12458,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>1</v>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2268,7 +2272,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2369,7 +2377,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -9022,7 +9034,11 @@
       <c r="AB81" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC81" s="4" t="inlineStr"/>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9935,7 +9951,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10856,7 +10876,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -11365,7 +11389,11 @@
       <c r="AB104" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -12496,7 +12524,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -13833,7 +13865,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14342,7 +14378,11 @@
       <c r="AB133" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14956,7 +14996,11 @@
       <c r="AB139" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC139" s="4" t="inlineStr"/>
+      <c r="AC139" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -15162,7 +15206,11 @@
       <c r="AB141" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC141" s="4" t="inlineStr"/>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -16091,7 +16139,11 @@
       <c r="AB150" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC150" s="4" t="inlineStr"/>
+      <c r="AC150" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -16495,7 +16547,11 @@
       <c r="AB154" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC154" s="4" t="inlineStr"/>
+      <c r="AC154" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 66 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2657,8 +2657,8 @@
       <c r="S19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3390,8 +3390,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3495,8 +3495,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6161,8 +6161,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6921,13 +6921,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6977,8 +6977,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7051,8 +7051,8 @@
       <c r="P62" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" s="9" t="n">
-        <v>1</v>
+      <c r="Q62" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>0</v>
@@ -7782,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9740,8 +9740,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -12178,7 +12178,7 @@
         <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12253,13 +12253,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>6</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12485,8 +12485,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P115" s="9" t="n">
-        <v>3</v>
+      <c r="P115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>1</v>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12826,8 +12826,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -13168,7 +13168,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13226,8 +13226,8 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>3</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13736,8 +13736,8 @@
       <c r="T127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U127" s="9" t="n">
-        <v>0</v>
+      <c r="U127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V127" s="9" t="n">
         <v>0</v>
@@ -13842,7 +13842,7 @@
         <v>1</v>
       </c>
       <c r="U128" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V128" s="10" t="n">
         <v>4</v>
@@ -15276,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
@@ -15483,10 +15483,10 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" s="9" t="n">
         <v>0</v>
@@ -15547,7 +15547,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15599,8 +15599,8 @@
       <c r="S145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16410,8 +16410,8 @@
       <c r="P153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" s="9" t="n">
-        <v>0</v>
+      <c r="Q153" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16511,8 +16511,8 @@
       <c r="P154" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q154" s="9" t="n">
-        <v>0</v>
+      <c r="Q154" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -17564,7 +17564,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17630,7 +17630,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17795,7 +17795,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17861,7 +17861,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -18224,7 +18224,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -18290,7 +18290,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -18323,7 +18323,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -18455,7 +18455,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -18488,7 +18488,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -18521,7 +18521,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 29 clubs short</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1229,8 +1229,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1847,8 +1847,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2140,8 +2140,8 @@
       <c r="S14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="9" t="n">
-        <v>0</v>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2574,8 +2574,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3289,8 +3289,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3489,8 +3489,8 @@
       <c r="W27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>3</v>
+      <c r="X27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3600,8 +3600,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4214,8 +4214,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4521,8 +4521,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="9" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5753,8 +5753,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6464,8 +6464,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6876,8 +6876,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6971,8 +6971,8 @@
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X61" s="9" t="n">
-        <v>3</v>
+      <c r="X61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7280,8 +7280,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7486,8 +7486,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7688,8 +7688,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8411,8 +8411,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9433,8 +9433,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9991,17 +9991,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10035,11 +10035,11 @@
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="9" t="n">
-        <v>3</v>
+      <c r="V91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>7</v>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10152,8 +10152,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10183,7 +10183,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10224,7 +10224,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>0</v>
@@ -10235,8 +10235,8 @@
       <c r="S93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
@@ -10253,8 +10253,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10344,7 +10344,7 @@
         <v>1</v>
       </c>
       <c r="U94" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V94" s="9" t="n">
         <v>0</v>
@@ -10358,8 +10358,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10463,8 +10463,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10972,8 +10972,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -11044,10 +11044,10 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11279,8 +11279,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11568,8 +11568,8 @@
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
@@ -11586,8 +11586,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -12962,7 +12962,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12976,13 +12976,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13023,8 +13023,8 @@
       <c r="V120" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W120" s="9" t="n">
-        <v>3</v>
+      <c r="W120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>4</v>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13751,8 +13751,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13992,7 +13992,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14062,8 +14062,8 @@
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14163,8 +14163,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14505,7 +14505,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14575,8 +14575,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -15232,7 +15232,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15302,8 +15302,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -15337,7 +15337,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15407,8 +15407,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15749,7 +15749,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15801,11 +15801,11 @@
       <c r="S147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" s="9" t="n">
-        <v>0</v>
+      <c r="T147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V147" s="9" t="n">
         <v>0</v>
@@ -15819,8 +15819,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -15973,13 +15973,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -16524,7 +16524,7 @@
         <v>1</v>
       </c>
       <c r="U154" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V154" s="9" t="n">
         <v>1</v>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17055,8 +17055,8 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -17086,7 +17086,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17156,8 +17156,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -17465,7 +17465,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -17531,7 +17531,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -17564,7 +17564,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17597,7 +17597,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -17630,7 +17630,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17663,7 +17663,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17696,7 +17696,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -17762,7 +17762,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17795,7 +17795,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17861,7 +17861,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17894,7 +17894,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -17960,7 +17960,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18026,7 +18026,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -18074,7 +18074,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -18092,7 +18092,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -18125,7 +18125,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -18158,7 +18158,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -18191,7 +18191,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -18257,7 +18257,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -18323,7 +18323,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -18356,7 +18356,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -18389,7 +18389,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -18422,7 +18422,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -18455,7 +18455,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 29 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 29 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -967,17 +967,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="8" t="n">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
+        <v>-15</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2249,13 +2249,13 @@
         <v>1</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -2312,17 +2312,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2768,8 +2768,8 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>3</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3128,13 +3128,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>2</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3233,13 +3233,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3439,17 +3439,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3851,13 +3851,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4259,13 +4259,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4360,13 +4360,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4465,13 +4465,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4566,17 +4566,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4595,8 +4595,8 @@
       <c r="P38" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" s="9" t="n">
-        <v>1</v>
+      <c r="Q38" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4671,17 +4671,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5079,13 +5079,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5184,17 +5184,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5491,13 +5491,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5596,13 +5596,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5640,8 +5640,8 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>3</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>2</v>
       </c>
       <c r="R50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="9" t="n">
         <v>1</v>
@@ -5845,8 +5845,8 @@
       <c r="V50" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W50" s="9" t="n">
-        <v>2</v>
+      <c r="W50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X50" s="9" t="n">
         <v>3</v>
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6004,13 +6004,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6206,13 +6206,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6307,17 +6307,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6355,7 +6355,7 @@
         <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>4</v>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6509,13 +6509,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6654,8 +6654,8 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>2</v>
+      <c r="V58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6756,14 +6756,14 @@
       <c r="T59" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="9" t="n">
-        <v>2</v>
+      <c r="U59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>6</v>
@@ -6820,13 +6820,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6921,13 +6921,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7022,13 +7022,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7123,13 +7123,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7224,13 +7224,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7329,13 +7329,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7430,13 +7430,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7531,13 +7531,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7632,17 +7632,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7676,11 +7676,11 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>0</v>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>4</v>
@@ -7842,13 +7842,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7943,13 +7943,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8044,13 +8044,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8145,17 +8145,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8190,7 +8190,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8250,13 +8250,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8456,13 +8456,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8557,17 +8557,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8601,8 +8601,8 @@
       <c r="U77" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>2</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8662,13 +8662,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8763,17 +8763,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8868,13 +8868,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8969,13 +8969,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>6</v>
@@ -9074,13 +9074,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9175,13 +9175,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9276,13 +9276,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9377,13 +9377,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9579,17 +9579,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9684,17 +9684,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9785,13 +9785,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9886,13 +9886,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9918,8 +9918,8 @@
       <c r="Q90" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R90" s="9" t="n">
-        <v>1</v>
+      <c r="R90" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S90" s="9" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>7</v>
@@ -9991,17 +9991,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10096,13 +10096,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10197,13 +10197,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10302,17 +10302,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10407,13 +10407,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10508,13 +10508,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10609,13 +10609,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10710,13 +10710,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10811,13 +10811,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10855,8 +10855,8 @@
       <c r="U99" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>1</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>2</v>
       </c>
       <c r="S100" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
@@ -10961,7 +10961,7 @@
         <v>3</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11118,17 +11118,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11223,17 +11223,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11268,7 +11268,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11324,13 +11324,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11429,13 +11429,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11530,13 +11530,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11631,13 +11631,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>1</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11722,7 +11722,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11736,17 +11736,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11765,8 +11765,8 @@
       <c r="P108" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" s="9" t="n">
-        <v>1</v>
+      <c r="Q108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11841,13 +11841,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11885,11 +11885,11 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>0</v>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>4</v>
@@ -11942,17 +11942,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11987,7 +11987,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12047,13 +12047,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12085,14 +12085,14 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>2</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12148,13 +12148,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12239,7 +12239,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12253,13 +12253,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12300,8 +12300,8 @@
       <c r="V113" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W113" s="9" t="n">
-        <v>1</v>
+      <c r="W113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>6</v>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12358,13 +12358,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12402,11 +12402,11 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" s="9" t="n">
-        <v>0</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W114" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X114" s="9" t="n">
         <v>0</v>
@@ -12459,13 +12459,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="P115" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>1</v>
@@ -12504,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12564,13 +12564,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12669,17 +12669,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12770,13 +12770,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12871,13 +12871,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12918,8 +12918,8 @@
       <c r="V119" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W119" s="9" t="n">
-        <v>0</v>
+      <c r="W119" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>6</v>
@@ -12976,13 +12976,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>4</v>
       </c>
       <c r="W120" s="10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>4</v>
@@ -13081,13 +13081,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -13229,8 +13229,8 @@
       <c r="V122" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W122" s="9" t="n">
-        <v>0</v>
+      <c r="W122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X122" s="9" t="n">
         <v>0</v>
@@ -13283,13 +13283,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13310,10 +13310,10 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X123" s="9" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13388,17 +13388,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13432,8 +13432,8 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>2</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13493,13 +13493,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13594,13 +13594,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13695,17 +13695,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13800,13 +13800,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>4</v>
@@ -13905,13 +13905,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -14006,17 +14006,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -14051,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14107,17 +14107,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -14151,11 +14151,11 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>0</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>6</v>
@@ -14212,13 +14212,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14313,13 +14313,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -14519,17 +14519,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14564,7 +14564,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14830,13 +14830,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14931,13 +14931,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -15036,17 +15036,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -15141,17 +15141,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -15246,17 +15246,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -15291,7 +15291,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15337,7 +15337,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15351,13 +15351,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15389,14 +15389,14 @@
       <c r="S143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15456,17 +15456,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -15501,7 +15501,7 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15561,13 +15561,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15662,13 +15662,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15763,17 +15763,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
@@ -15808,7 +15808,7 @@
         <v>1</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15868,13 +15868,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15959,7 +15959,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15973,13 +15973,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -16017,11 +16017,11 @@
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="9" t="n">
+      <c r="V149" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W149" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W149" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>4</v>
@@ -16074,13 +16074,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16179,13 +16179,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -16280,13 +16280,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -16381,13 +16381,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16482,13 +16482,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q154" s="10" t="n">
         <v>2</v>
@@ -16526,11 +16526,11 @@
       <c r="U154" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W154" s="9" t="n">
-        <v>0</v>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W154" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>6</v>
@@ -16587,17 +16587,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -16688,17 +16688,17 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L156" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M156" s="8" t="n">
@@ -16733,7 +16733,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16793,13 +16793,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -16894,13 +16894,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16999,17 +16999,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -17044,7 +17044,7 @@
         <v>1</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -17100,17 +17100,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17130,13 +17130,13 @@
         <v>0</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" s="9" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
         <v>0</v>
       </c>
       <c r="V160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -17205,13 +17205,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>0</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
@@ -17250,7 +17250,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
@@ -17350,11 +17350,11 @@
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" s="9" t="n">
-        <v>0</v>
+      <c r="V162" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W162" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X162" s="10" t="n">
         <v>6</v>
@@ -17480,7 +17480,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -17513,7 +17513,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -17531,13 +17531,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -17579,7 +17579,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -17597,7 +17597,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -17645,7 +17645,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -17696,7 +17696,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -17744,7 +17744,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -17762,7 +17762,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17810,7 +17810,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -17828,7 +17828,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17894,7 +17894,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -17909,7 +17909,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -17942,7 +17942,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -17960,13 +17960,13 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -18008,7 +18008,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -18059,7 +18059,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -18074,7 +18074,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -18107,7 +18107,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -18125,7 +18125,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -18173,7 +18173,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -18191,7 +18191,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>2.17</v>
+        <v>2.83</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -18206,7 +18206,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -18224,7 +18224,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -18290,7 +18290,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -18305,7 +18305,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -18338,7 +18338,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -18356,7 +18356,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -18371,7 +18371,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -18404,7 +18404,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -18422,7 +18422,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -18437,7 +18437,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -18470,7 +18470,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -18488,7 +18488,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -18521,13 +18521,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -18536,7 +18536,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -18554,7 +18554,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -18569,7 +18569,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 29 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 29 clubs short</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -1005,8 +1005,8 @@
       <c r="S3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="9" t="n">
-        <v>0</v>
+      <c r="T3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
@@ -1017,8 +1017,8 @@
       <c r="W3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X3" s="9" t="n">
-        <v>3</v>
+      <c r="X3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1405,13 +1405,13 @@
         <v>4</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="9" t="n">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2233,8 +2233,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P15" s="9" t="n">
-        <v>3</v>
+      <c r="P15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>1</v>
@@ -2254,8 +2254,8 @@
       <c r="V15" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W15" s="9" t="n">
-        <v>1</v>
+      <c r="W15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="9" t="n">
         <v>0</v>
@@ -3851,13 +3851,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="10" t="n">
         <v>1</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5222,8 +5222,8 @@
       <c r="S44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="10" t="n">
         <v>2</v>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6134,8 +6134,8 @@
       <c r="P53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" s="9" t="n">
-        <v>1</v>
+      <c r="Q53" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>4</v>
@@ -7329,13 +7329,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7531,13 +7531,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -8145,13 +8145,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8250,13 +8250,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9276,13 +9276,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9320,8 +9320,8 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>2</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9785,13 +9785,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9886,13 +9886,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>3</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" s="10" t="n">
         <v>1</v>
@@ -9991,13 +9991,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10609,13 +10609,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10656,8 +10656,8 @@
       <c r="V97" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W97" s="9" t="n">
-        <v>0</v>
+      <c r="W97" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>4</v>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10811,13 +10811,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10840,14 +10840,14 @@
       <c r="P99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" s="9" t="n">
-        <v>1</v>
+      <c r="Q99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="10" t="n">
         <v>1</v>
@@ -10859,7 +10859,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>4</v>
@@ -11351,13 +11351,13 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S104" s="9" t="n">
         <v>0</v>
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>1</v>
@@ -12358,13 +12358,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>4</v>
       </c>
       <c r="W114" s="10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="X114" s="9" t="n">
         <v>0</v>
@@ -12669,13 +12669,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12808,8 +12808,8 @@
       <c r="S118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
@@ -12976,13 +12976,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -13024,7 +13024,7 @@
         <v>4</v>
       </c>
       <c r="W120" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>4</v>
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13800,13 +13800,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -14107,13 +14107,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>6</v>
@@ -14657,10 +14657,10 @@
         <v>2</v>
       </c>
       <c r="R136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" s="10" t="n">
         <v>1</v>
@@ -15547,7 +15547,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15561,13 +15561,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15602,8 +15602,8 @@
       <c r="T145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U145" s="9" t="n">
-        <v>0</v>
+      <c r="U145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V145" s="9" t="n">
         <v>0</v>
@@ -15763,13 +15763,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16587,17 +16587,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L155" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -16631,11 +16631,11 @@
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W155" s="9" t="n">
-        <v>0</v>
+      <c r="V155" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W155" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X155" s="10" t="n">
         <v>4</v>
@@ -16674,7 +16674,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16688,13 +16688,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16732,8 +16732,8 @@
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="9" t="n">
-        <v>3</v>
+      <c r="V156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -17205,13 +17205,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>4</v>
       </c>
       <c r="W162" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X162" s="10" t="n">
         <v>6</v>
@@ -17465,7 +17465,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -17531,7 +17531,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -17729,7 +17729,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -17795,7 +17795,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18026,7 +18026,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -18125,13 +18125,13 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -18455,7 +18455,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -18521,7 +18521,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -18536,7 +18536,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">

--- a/docs/d/61/inyear.xlsx
+++ b/docs/d/61/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 29 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 29 clubs short</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2030,8 +2030,8 @@
       <c r="P13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="9" t="n">
-        <v>1</v>
+      <c r="Q13" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2648,8 +2648,8 @@
       <c r="P19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" s="9" t="n">
-        <v>1</v>
+      <c r="Q19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="10" t="n">
         <v>2</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>1</v>
@@ -6004,13 +6004,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6509,13 +6509,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>6</v>
@@ -6820,13 +6820,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -7055,10 +7055,10 @@
         <v>2</v>
       </c>
       <c r="R62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="10" t="n">
         <v>1</v>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7943,13 +7943,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7987,11 +7987,11 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>3</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>6</v>
@@ -8355,13 +8355,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="U77" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V77" s="10" t="n">
         <v>4</v>
@@ -8662,13 +8662,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -9785,13 +9785,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9886,13 +9886,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9933,8 +9933,8 @@
       <c r="V90" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W90" s="9" t="n">
-        <v>3</v>
+      <c r="W90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>7</v>
@@ -9991,13 +9991,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>7</v>
@@ -10811,13 +10811,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10942,8 +10942,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P100" s="9" t="n">
-        <v>3</v>
+      <c r="P100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q100" s="10" t="n">
         <v>2</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11118,17 +11118,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L102" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11162,11 +11162,11 @@
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="9" t="n">
-        <v>1</v>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>4</v>
@@ -11429,13 +11429,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11530,13 +11530,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11783,8 +11783,8 @@
       <c r="V108" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>3</v>
+      <c r="W108" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>5</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11942,13 +11942,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11978,16 +11978,16 @@
         <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12253,13 +12253,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>4</v>
       </c>
       <c r="W113" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>6</v>
@@ -12871,13 +12871,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>4</v>
       </c>
       <c r="W119" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>6</v>
@@ -12976,13 +12976,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>4</v>
       </c>
       <c r="W120" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>4</v>
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13388,13 +13388,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13493,13 +13493,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13594,13 +13594,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13695,13 +13695,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>1</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13786,7 +13786,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13800,13 +13800,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q128" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R128" s="9" t="n">
-        <v>1</v>
+      <c r="R128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S128" s="9" t="n">
         <v>1</v>
@@ -13848,7 +13848,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>4</v>
@@ -14107,13 +14107,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>6</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -15036,13 +15036,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15141,13 +15141,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>1</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -15381,7 +15381,7 @@
         <v>0</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -15973,13 +15973,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>4</v>
       </c>
       <c r="W149" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>4</v>
@@ -16110,7 +16110,7 @@
         <v>0</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -16587,13 +16587,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -16614,10 +16614,10 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
@@ -16635,7 +16635,7 @@
         <v>4</v>
       </c>
       <c r="W155" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X155" s="10" t="n">
         <v>4</v>
@@ -16999,13 +16999,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>1</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -17531,7 +17531,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -17564,7 +17564,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17927,7 +17927,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -18125,7 +18125,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
@@ -18158,7 +18158,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -18173,7 +18173,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -18191,7 +18191,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -18323,7 +18323,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
